--- a/artfynd/A 29419-2026 artfynd.xlsx
+++ b/artfynd/A 29419-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>132371367</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29419-2026 artfynd.xlsx
+++ b/artfynd/A 29419-2026 artfynd.xlsx
@@ -952,11 +952,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 29419-2026 artfynd.xlsx
+++ b/artfynd/A 29419-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>132371367</v>
       </c>
       <c r="B4" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
